--- a/artfynd/A 56755-2021 artfynd.xlsx
+++ b/artfynd/A 56755-2021 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Maja Wressel, Nils Bodin</t>
+          <t>Nils Bodin, Maja Wressel</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 56755-2021 artfynd.xlsx
+++ b/artfynd/A 56755-2021 artfynd.xlsx
@@ -774,7 +774,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Nils Bodin, Maja Wressel</t>
+          <t>Maja Wressel, Nils Bodin</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 56755-2021 artfynd.xlsx
+++ b/artfynd/A 56755-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136894122</v>
       </c>
       <c r="B2" t="n">
-        <v>93449</v>
+        <v>93451</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56755-2021 artfynd.xlsx
+++ b/artfynd/A 56755-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136894122</v>
       </c>
       <c r="B2" t="n">
-        <v>93451</v>
+        <v>93453</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56755-2021 artfynd.xlsx
+++ b/artfynd/A 56755-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136894122</v>
       </c>
       <c r="B2" t="n">
-        <v>93453</v>
+        <v>93454</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56755-2021 artfynd.xlsx
+++ b/artfynd/A 56755-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136894122</v>
       </c>
       <c r="B2" t="n">
-        <v>93454</v>
+        <v>93460</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 56755-2021 artfynd.xlsx
+++ b/artfynd/A 56755-2021 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136894122</v>
       </c>
       <c r="B2" t="n">
-        <v>93460</v>
+        <v>93464</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
